--- a/docs/vehicle-import/vehicle-import-template.xlsx
+++ b/docs/vehicle-import/vehicle-import-template.xlsx
@@ -89,7 +89,7 @@
     <t>الأعمدة المطلوبة (بالأصفر): رقم اللوحة، الشركة المصنعة، الطراز. بقية الأعمدة اختيارية ولا تُملأ تلقائيًا.</t>
   </si>
   <si>
-    <t>المشروع: اكتب اسم المشروع كما هو في النظام. يُرفض الصف إذا لم يوجد المشروع أو لم تكن لك صلاحية الإضافة إليه.</t>
+    <t>المشروع (اختياري): اكتب اسم المشروع كما هو في النظام لربط المركبة به. إذا لم يوجد المشروع أو لم تكن لك صلاحية الإضافة إليه تُستورد المركبة بدون مشروع ويُحفظ اسمه في الملاحظات لتسنده لاحقًا من شاشة المركبات (من لا يحق له إضافة مركبة بدون مشروع، مثل مدير المشروع، يُرفض صفه). لا تُنشأ مشاريع جديدة.</t>
   </si>
   <si>
     <t>الحالة: متاحة، خارج الخدمة، مباعة (أو اتركها فارغة). نوع الوقود: بنزين، ديزل، هجين، كهرباء، غاز ويُحفظ ضمن الملاحظات.</t>
